--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484627_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484627_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.328</v>
+        <v>9.266999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>7.0128</v>
+        <v>6.2986</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3152</v>
+        <v>2.9684</v>
       </c>
       <c r="G2" t="n">
         <v>4.511</v>
@@ -610,13 +610,13 @@
         <v>0.733</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4822</v>
+        <v>1.4212</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5008</v>
+        <v>0.7866</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9814000000000001</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>4.4344</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. CASASUS GOYENECHE</t>
+          <t>F. FERRER I SEGURA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.9834</v>
+        <v>8.286300000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7283</v>
+        <v>4.9406</v>
       </c>
       <c r="F3" t="n">
-        <v>3.255</v>
+        <v>3.3456</v>
       </c>
       <c r="G3" t="n">
-        <v>3.6671</v>
+        <v>5.1226</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5069</v>
+        <v>4.2026</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1602</v>
+        <v>0.92</v>
       </c>
       <c r="J3" t="n">
-        <v>2.364</v>
+        <v>4.6055</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5882</v>
+        <v>4.4866</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7759</v>
+        <v>0.119</v>
       </c>
       <c r="M3" t="n">
-        <v>1.303</v>
+        <v>0.517</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9187</v>
+        <v>-0.284</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3843</v>
+        <v>0.8011</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0158</v>
+        <v>2.5656</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0158</v>
+        <v>2.5656</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0335</v>
+        <v>-0.0458</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0973</v>
+        <v>-0.3088</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0638</v>
+        <v>0.263</v>
       </c>
       <c r="V3" t="n">
-        <v>1.267</v>
+        <v>0.6439</v>
       </c>
       <c r="W3" t="n">
-        <v>1.267</v>
+        <v>0.6439</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F. FERRER I SEGURA</t>
+          <t>G. CASASUS GOYENECHE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>7.3293</v>
+        <v>7.4589</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4048</v>
+        <v>4.0552</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9245</v>
+        <v>3.4037</v>
       </c>
       <c r="G4" t="n">
-        <v>5.1226</v>
+        <v>3.6671</v>
       </c>
       <c r="H4" t="n">
-        <v>4.2026</v>
+        <v>2.5069</v>
       </c>
       <c r="I4" t="n">
-        <v>0.92</v>
+        <v>1.1602</v>
       </c>
       <c r="J4" t="n">
-        <v>4.6055</v>
+        <v>2.364</v>
       </c>
       <c r="K4" t="n">
-        <v>4.4866</v>
+        <v>1.5882</v>
       </c>
       <c r="L4" t="n">
-        <v>0.119</v>
+        <v>0.7759</v>
       </c>
       <c r="M4" t="n">
-        <v>0.517</v>
+        <v>1.303</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.284</v>
+        <v>0.9187</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8011</v>
+        <v>0.3843</v>
       </c>
       <c r="P4" t="n">
-        <v>2.5656</v>
+        <v>2.0158</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5656</v>
+        <v>2.0158</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0028</v>
+        <v>0.509</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8446</v>
+        <v>0.4242</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1582</v>
+        <v>0.0848</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6439</v>
+        <v>1.267</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6439</v>
+        <v>1.267</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>6.8939</v>
+        <v>5.7758</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1374</v>
+        <v>2.0937</v>
       </c>
       <c r="F5" t="n">
-        <v>3.7564</v>
+        <v>3.6821</v>
       </c>
       <c r="G5" t="n">
         <v>2.915</v>
@@ -844,13 +844,13 @@
         <v>2.7489</v>
       </c>
       <c r="S5" t="n">
-        <v>1.7461</v>
+        <v>0.628</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5362</v>
+        <v>0.4925</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2098</v>
+        <v>0.1355</v>
       </c>
       <c r="V5" t="n">
         <v>2.2328</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.7182</v>
+        <v>4.1301</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7943</v>
+        <v>1.3301</v>
       </c>
       <c r="F6" t="n">
-        <v>2.9239</v>
+        <v>2.8</v>
       </c>
       <c r="G6" t="n">
         <v>-2.1661</v>
@@ -922,13 +922,13 @@
         <v>1.4661</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2666</v>
+        <v>0.6785</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3673</v>
+        <v>0.1686</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6338</v>
+        <v>0.51</v>
       </c>
       <c r="V6" t="n">
         <v>5.0679</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ NARRO</t>
+          <t>R. RAMOS SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.2337</v>
+        <v>3.8766</v>
       </c>
       <c r="E7" t="n">
-        <v>2.3685</v>
+        <v>0.9145</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8651</v>
+        <v>2.9622</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0152</v>
+        <v>0.5446</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3773</v>
+        <v>0.8522</v>
       </c>
       <c r="I7" t="n">
-        <v>0.362</v>
+        <v>-0.3076</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4943</v>
+        <v>0.3466</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1051</v>
+        <v>0.2693</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5994</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>0.479</v>
+        <v>0.198</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4824</v>
+        <v>0.583</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9614</v>
+        <v>-0.3849</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3665</v>
+        <v>2.3823</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3665</v>
+        <v>2.3823</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3484</v>
+        <v>0.3162</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3288</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0196</v>
+        <v>0.3818</v>
       </c>
       <c r="V7" t="n">
-        <v>2.5339</v>
+        <v>0.6335</v>
       </c>
       <c r="W7" t="n">
-        <v>2.5339</v>
+        <v>0.6335</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. RAMOS SAN SEBASTIAN</t>
+          <t>D. FERNANDEZ NARRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3.0712</v>
+        <v>3.0413</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2825</v>
+        <v>2.1762</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7887</v>
+        <v>0.8651</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5446</v>
+        <v>-0.0152</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8522</v>
+        <v>-0.3773</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3076</v>
+        <v>0.362</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3466</v>
+        <v>-0.4943</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2693</v>
+        <v>0.1051</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07729999999999999</v>
+        <v>-0.5994</v>
       </c>
       <c r="M8" t="n">
-        <v>0.198</v>
+        <v>0.479</v>
       </c>
       <c r="N8" t="n">
-        <v>0.583</v>
+        <v>-0.4824</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3849</v>
+        <v>0.9614</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3823</v>
+        <v>0.3665</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3823</v>
+        <v>0.3665</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4892</v>
+        <v>0.1561</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6976</v>
+        <v>0.1365</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2084</v>
+        <v>0.0196</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6335</v>
+        <v>2.5339</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6335</v>
+        <v>2.5339</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.4282</v>
+        <v>3.022</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4798</v>
+        <v>0.9745</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9484</v>
+        <v>2.0475</v>
       </c>
       <c r="G9" t="n">
         <v>3.2988</v>
@@ -1156,13 +1156,13 @@
         <v>2.0158</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7032</v>
+        <v>-0.1094</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4774</v>
+        <v>0.0174</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2258</v>
+        <v>-0.1267</v>
       </c>
       <c r="V9" t="n">
         <v>-1.267</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. ROSELLO ORTS</t>
+          <t>C. FAJARDO PAÑOS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8026</v>
+        <v>0.6251</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5541</v>
+        <v>0.6251</v>
       </c>
       <c r="F10" t="n">
-        <v>3.3567</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.929</v>
+        <v>0.6251</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4431</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3721</v>
+        <v>0.6251</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8217</v>
+        <v>0.6251</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2936</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.1154</v>
+        <v>0.6251</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1072</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1495</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2567</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.4661</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3.2986</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5875</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2217</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8092</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. FAJARDO PAÑOS</t>
+          <t>P. ROSELLO ORTS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6251</v>
+        <v>0.3622</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6251</v>
+        <v>-2.499</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>2.8612</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6251</v>
+        <v>-0.929</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.4431</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6251</v>
+        <v>-1.3721</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6251</v>
+        <v>-0.8217</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>0.2936</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6251</v>
+        <v>-1.1154</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>-0.1072</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>0.1495</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-0.2567</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.4661</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3.2986</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>0.1471</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>-0.1666</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>0.3137</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.4396</v>
+        <v>-0.1208</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.9161</v>
+        <v>-1.5726</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4765</v>
+        <v>1.4518</v>
       </c>
       <c r="G12" t="n">
         <v>1.0082</v>
@@ -1390,13 +1390,13 @@
         <v>1.2828</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2541</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2753</v>
+        <v>0.0683</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0212</v>
+        <v>-0.0036</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6439</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.1995</v>
+        <v>-0.3997</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.0619</v>
+        <v>-1.485</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8624000000000001</v>
+        <v>1.0853</v>
       </c>
       <c r="G13" t="n">
         <v>-2.1363</v>
@@ -1468,13 +1468,13 @@
         <v>1.2828</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3461</v>
+        <v>0.4538</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3122</v>
+        <v>0.2647</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0339</v>
+        <v>0.1891</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>44.7745</v>
+        <v>45.3248</v>
       </c>
       <c r="E14" t="n">
-        <v>17.3014</v>
+        <v>17.8519</v>
       </c>
       <c r="F14" t="n">
-        <v>27.4728</v>
+        <v>27.4729</v>
       </c>
       <c r="G14" t="n">
         <v>16.4458</v>
@@ -1516,7 +1516,7 @@
         <v>14.6833</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7623</v>
+        <v>1.762299999999999</v>
       </c>
       <c r="J14" t="n">
         <v>8.978</v>
@@ -1525,7 +1525,7 @@
         <v>8.6555</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3227000000000001</v>
+        <v>0.3226999999999999</v>
       </c>
       <c r="M14" t="n">
         <v>7.4674</v>
@@ -1546,13 +1546,13 @@
         <v>20.1582</v>
       </c>
       <c r="S14" t="n">
-        <v>3.668900000000001</v>
+        <v>4.2194</v>
       </c>
       <c r="T14" t="n">
-        <v>1.267</v>
+        <v>1.8178</v>
       </c>
       <c r="U14" t="n">
-        <v>2.4017</v>
+        <v>2.4018</v>
       </c>
       <c r="V14" t="n">
         <v>14.5806</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.903</v>
+        <v>0.887</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1838</v>
+        <v>-0.1047</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7192</v>
+        <v>0.9917</v>
       </c>
       <c r="G15" t="n">
         <v>0.3721</v>
@@ -1624,13 +1624,13 @@
         <v>0.733</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3634</v>
+        <v>0.3475</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6395</v>
+        <v>0.3511</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2761</v>
+        <v>-0.0036</v>
       </c>
       <c r="V15" t="n">
         <v>1.267</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.1675</v>
+        <v>-1.1704</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1303</v>
+        <v>0.2265</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2978</v>
+        <v>-1.3969</v>
       </c>
       <c r="G16" t="n">
         <v>0.08400000000000001</v>
@@ -1702,13 +1702,13 @@
         <v>0.733</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3956</v>
+        <v>-0.3986</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6056</v>
+        <v>-0.5094</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2099</v>
+        <v>0.1108</v>
       </c>
       <c r="V16" t="n">
         <v>-1.5889</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. CABRERA GONZALEZ</t>
+          <t>M. CISNEROS RUIZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.0932</v>
+        <v>-1.7752</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.8448</v>
+        <v>-0.5101</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2484</v>
+        <v>-1.2651</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.3897</v>
+        <v>-1.5978</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8416</v>
+        <v>-0.9956</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5481</v>
+        <v>-0.6022</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6719000000000001</v>
+        <v>-0.3747</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1241</v>
+        <v>-0.446</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5478</v>
+        <v>0.0712</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7178</v>
+        <v>-1.2231</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7175</v>
+        <v>-0.5496</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0003</v>
+        <v>-0.6735</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3665</v>
+        <v>1.0995</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4661</v>
+        <v>1.0995</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.3214</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0392</v>
+        <v>-0.1353</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0308</v>
+        <v>-0.1861</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.267</v>
+        <v>-0.9554</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3011</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.9658</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. MEDINA LERMA</t>
+          <t>F. BLASCO MANZANO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.2146</v>
+        <v>-3.3023</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0229</v>
+        <v>-3.7853</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.1917</v>
+        <v>0.483</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2265</v>
+        <v>-3.517</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2223</v>
+        <v>-1.5297</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4488</v>
+        <v>-1.9873</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9122</v>
+        <v>-2.5825</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4952</v>
+        <v>-0.8518</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4169</v>
+        <v>-1.7306</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6857</v>
+        <v>-0.9345</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7175</v>
+        <v>-0.6778</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0318</v>
+        <v>-0.2567</v>
       </c>
       <c r="P18" t="n">
-        <v>-3.8484</v>
+        <v>0.3665</v>
       </c>
       <c r="Q18" t="n">
-        <v>-4.5814</v>
+        <v>-0.9163</v>
       </c>
       <c r="R18" t="n">
-        <v>0.733</v>
+        <v>1.2828</v>
       </c>
       <c r="S18" t="n">
-        <v>1.6297</v>
+        <v>-0.1518</v>
       </c>
       <c r="T18" t="n">
-        <v>1.6463</v>
+        <v>-0.2865</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0166</v>
+        <v>0.1348</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.2224</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.2224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. CISNEROS RUIZ</t>
+          <t>S. CABRERA GONZALEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.2627</v>
+        <v>-3.4953</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5678</v>
+        <v>-3.3256</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6949</v>
+        <v>-0.1697</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.5978</v>
+        <v>-1.3897</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.9956</v>
+        <v>-0.8416</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6022</v>
+        <v>-0.5481</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3747</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.446</v>
+        <v>-0.1241</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0712</v>
+        <v>-0.5478</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2231</v>
+        <v>-0.7178</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5496</v>
+        <v>-0.7175</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6735</v>
+        <v>-0.0003</v>
       </c>
       <c r="P19" t="n">
-        <v>1.0995</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0995</v>
+        <v>1.4661</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.809</v>
+        <v>-0.4721</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.193</v>
+        <v>-0.52</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6159</v>
+        <v>0.0479</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9554</v>
+        <v>-1.267</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.3011</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.9554</v>
+        <v>-0.9658</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. BLASCO MANZANO</t>
+          <t>R. MEDINA LERMA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.3177</v>
+        <v>-4.1441</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.7468</v>
+        <v>-2.0806</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4292</v>
+        <v>-2.0635</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.517</v>
+        <v>1.2265</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.5297</v>
+        <v>-0.2223</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.9873</v>
+        <v>1.4488</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.5825</v>
+        <v>1.9122</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.8518</v>
+        <v>0.4952</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.7306</v>
+        <v>1.4169</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9345</v>
+        <v>-0.6857</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6778</v>
+        <v>-0.7175</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2567</v>
+        <v>0.0318</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3665</v>
+        <v>-3.8484</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9163</v>
+        <v>-4.5814</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2828</v>
+        <v>0.733</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1672</v>
+        <v>0.7002</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2481</v>
+        <v>0.5886</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0809</v>
+        <v>0.1116</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-2.2224</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.2224</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.7883</v>
+        <v>-6.3673</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.1161</v>
+        <v>-2.8276</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.6722</v>
+        <v>-3.5397</v>
       </c>
       <c r="G21" t="n">
         <v>-3.1273</v>
@@ -2092,13 +2092,13 @@
         <v>1.2828</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4936</v>
+        <v>-1.0726</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2662</v>
+        <v>-0.9777</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2274</v>
+        <v>-0.0948</v>
       </c>
       <c r="V21" t="n">
         <v>-2.5339</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. CARRION BALLESTER</t>
+          <t>A. SANCHEZ DE LA IGLESIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.5359</v>
+        <v>-7.7428</v>
       </c>
       <c r="E22" t="n">
-        <v>-8.223800000000001</v>
+        <v>-0.7449</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6879</v>
+        <v>-6.9979</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.7281</v>
+        <v>-0.6059</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.0517</v>
+        <v>-2.292</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.6764</v>
+        <v>1.6861</v>
       </c>
       <c r="J22" t="n">
-        <v>-4.0972</v>
+        <v>0.7359</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.7096</v>
+        <v>-0.5977</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.3876</v>
+        <v>1.3336</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6309</v>
+        <v>-1.3418</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3421</v>
+        <v>-1.6943</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2888</v>
+        <v>0.3525</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.2986</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.5814</v>
+        <v>-0.9163</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2828</v>
+        <v>0.733</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4908</v>
+        <v>-0.6188</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4548</v>
+        <v>-0.5645</v>
       </c>
       <c r="U22" t="n">
-        <v>0.036</v>
+        <v>-0.0543</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-6.3349</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-6.3349</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. SANCHEZ DE LA IGLESIA</t>
+          <t>S. CARRION BALLESTER</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.8389</v>
+        <v>-7.8623</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.841</v>
+        <v>-8.6084</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.9979</v>
+        <v>0.7461</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.6059</v>
+        <v>-4.7281</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.292</v>
+        <v>-2.0517</v>
       </c>
       <c r="I23" t="n">
-        <v>1.6861</v>
+        <v>-2.6764</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7359</v>
+        <v>-4.0972</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.5977</v>
+        <v>-1.7096</v>
       </c>
       <c r="L23" t="n">
-        <v>1.3336</v>
+        <v>-2.3876</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3418</v>
+        <v>-0.6309</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.6943</v>
+        <v>-0.3421</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3525</v>
+        <v>-0.2888</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.1833</v>
+        <v>-3.2986</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9163</v>
+        <v>-4.5814</v>
       </c>
       <c r="R23" t="n">
-        <v>0.733</v>
+        <v>1.2828</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7149</v>
+        <v>0.1644</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6606</v>
+        <v>0.0702</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0543</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>-6.3349</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-6.3349</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.458500000000001</v>
+        <v>-8.5197</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.6906</v>
+        <v>-6.9791</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.7679</v>
+        <v>-1.5406</v>
       </c>
       <c r="G24" t="n">
         <v>-3.1625</v>
@@ -2326,13 +2326,13 @@
         <v>0.733</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5026</v>
+        <v>-0.5637</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1297</v>
+        <v>-0.4182</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3729</v>
+        <v>-0.1456</v>
       </c>
       <c r="V24" t="n">
         <v>-0.945</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-44.7743</v>
+        <v>-43.4924</v>
       </c>
       <c r="E25" t="n">
-        <v>-28.7397</v>
+        <v>-28.7398</v>
       </c>
       <c r="F25" t="n">
-        <v>-16.0345</v>
+        <v>-14.7526</v>
       </c>
       <c r="G25" t="n">
         <v>-16.4457</v>
@@ -2377,7 +2377,7 @@
         <v>-1.7623</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.467499999999999</v>
+        <v>-7.4675</v>
       </c>
       <c r="K25" t="n">
         <v>-6.0281</v>
@@ -2404,13 +2404,13 @@
         <v>10.079</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.669</v>
+        <v>-2.3869</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.4018</v>
+        <v>-2.4017</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.2672</v>
+        <v>0.0149</v>
       </c>
       <c r="V25" t="n">
         <v>-14.5805</v>
